--- a/PickAndPlace_控制板pcb_2026_09_02.xlsx
+++ b/PickAndPlace_控制板pcb_2026_09_02.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_控制板pcb_2026_09_02" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_控制板pcb_2026_09_03" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="320">
   <si>
     <t>Designator</t>
   </si>
@@ -322,13 +322,13 @@
     <t>BUZ-TH_BD9.0-P4.00-D0.6-FD</t>
   </si>
   <si>
-    <t>65.151mm</t>
-  </si>
-  <si>
-    <t>74.549mm</t>
-  </si>
-  <si>
-    <t>67.151mm</t>
+    <t>67.437mm</t>
+  </si>
+  <si>
+    <t>75.057mm</t>
+  </si>
+  <si>
+    <t>69.437mm</t>
   </si>
   <si>
     <t>2.7kHz</t>
@@ -835,13 +835,10 @@
     <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
   </si>
   <si>
-    <t>54.737mm</t>
-  </si>
-  <si>
-    <t>75.057mm</t>
-  </si>
-  <si>
-    <t>55.737mm</t>
+    <t>53.848mm</t>
+  </si>
+  <si>
+    <t>54.848mm</t>
   </si>
   <si>
     <t>74.107mm</t>
@@ -959,6 +956,21 @@
   </si>
   <si>
     <t>32.14mm</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>59.563mm</t>
+  </si>
+  <si>
+    <t>77.216mm</t>
+  </si>
+  <si>
+    <t>57.413mm</t>
+  </si>
+  <si>
+    <t>77.207mm</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -3799,19 +3811,19 @@
         <v>274</v>
       </c>
       <c r="E53" t="s">
-        <v>275</v>
+        <v>104</v>
       </c>
       <c r="F53" t="s">
         <v>274</v>
       </c>
       <c r="G53" t="s">
+        <v>104</v>
+      </c>
+      <c r="H53" t="s">
         <v>275</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>276</v>
-      </c>
-      <c r="I53" t="s">
-        <v>277</v>
       </c>
       <c r="J53">
         <v>3</v>
@@ -3826,15 +3838,15 @@
         <v>22</v>
       </c>
       <c r="N53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O53" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B54" t="s">
         <v>213</v>
@@ -3843,22 +3855,22 @@
         <v>115</v>
       </c>
       <c r="D54" t="s">
+        <v>279</v>
+      </c>
+      <c r="E54" t="s">
         <v>280</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
+        <v>279</v>
+      </c>
+      <c r="G54" t="s">
+        <v>280</v>
+      </c>
+      <c r="H54" t="s">
         <v>281</v>
       </c>
-      <c r="F54" t="s">
+      <c r="I54" t="s">
         <v>280</v>
-      </c>
-      <c r="G54" t="s">
-        <v>281</v>
-      </c>
-      <c r="H54" t="s">
-        <v>282</v>
-      </c>
-      <c r="I54" t="s">
-        <v>281</v>
       </c>
       <c r="J54">
         <v>2</v>
@@ -3881,31 +3893,31 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>282</v>
+      </c>
+      <c r="B55" t="s">
         <v>283</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>284</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>285</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>286</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
+        <v>285</v>
+      </c>
+      <c r="G55" t="s">
+        <v>286</v>
+      </c>
+      <c r="H55" t="s">
         <v>287</v>
       </c>
-      <c r="F55" t="s">
-        <v>286</v>
-      </c>
-      <c r="G55" t="s">
-        <v>287</v>
-      </c>
-      <c r="H55" t="s">
+      <c r="I55" t="s">
         <v>288</v>
-      </c>
-      <c r="I55" t="s">
-        <v>289</v>
       </c>
       <c r="J55">
         <v>4</v>
@@ -3920,39 +3932,39 @@
         <v>22</v>
       </c>
       <c r="N55" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O55" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>290</v>
+      </c>
+      <c r="B56" t="s">
         <v>291</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>292</v>
-      </c>
-      <c r="C56" t="s">
-        <v>293</v>
       </c>
       <c r="D56" t="s">
         <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
       </c>
       <c r="G56" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H56" t="s">
         <v>26</v>
       </c>
       <c r="I56" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J56">
         <v>2</v>
@@ -3967,39 +3979,39 @@
         <v>22</v>
       </c>
       <c r="N56" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O56" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>295</v>
+      </c>
+      <c r="B57" t="s">
+        <v>291</v>
+      </c>
+      <c r="C57" t="s">
+        <v>292</v>
+      </c>
+      <c r="D57" t="s">
         <v>296</v>
       </c>
-      <c r="B57" t="s">
-        <v>292</v>
-      </c>
-      <c r="C57" t="s">
-        <v>293</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>297</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
+        <v>296</v>
+      </c>
+      <c r="G57" t="s">
+        <v>297</v>
+      </c>
+      <c r="H57" t="s">
+        <v>296</v>
+      </c>
+      <c r="I57" t="s">
         <v>298</v>
-      </c>
-      <c r="F57" t="s">
-        <v>297</v>
-      </c>
-      <c r="G57" t="s">
-        <v>298</v>
-      </c>
-      <c r="H57" t="s">
-        <v>297</v>
-      </c>
-      <c r="I57" t="s">
-        <v>299</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -4014,39 +4026,39 @@
         <v>22</v>
       </c>
       <c r="N57" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O57" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>299</v>
+      </c>
+      <c r="B58" t="s">
         <v>300</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>301</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>302</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>303</v>
       </c>
-      <c r="E58" t="s">
-        <v>304</v>
-      </c>
       <c r="F58" t="s">
+        <v>302</v>
+      </c>
+      <c r="G58" t="s">
         <v>303</v>
       </c>
-      <c r="G58" t="s">
-        <v>304</v>
-      </c>
       <c r="H58" t="s">
+        <v>302</v>
+      </c>
+      <c r="I58" t="s">
         <v>303</v>
-      </c>
-      <c r="I58" t="s">
-        <v>304</v>
       </c>
       <c r="J58">
         <v>1</v>
@@ -4061,39 +4073,39 @@
         <v>22</v>
       </c>
       <c r="N58" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O58" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>304</v>
+      </c>
+      <c r="B59" t="s">
+        <v>300</v>
+      </c>
+      <c r="C59" t="s">
+        <v>301</v>
+      </c>
+      <c r="D59" t="s">
         <v>305</v>
       </c>
-      <c r="B59" t="s">
-        <v>301</v>
-      </c>
-      <c r="C59" t="s">
-        <v>302</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>306</v>
       </c>
-      <c r="E59" t="s">
-        <v>307</v>
-      </c>
       <c r="F59" t="s">
+        <v>305</v>
+      </c>
+      <c r="G59" t="s">
         <v>306</v>
       </c>
-      <c r="G59" t="s">
-        <v>307</v>
-      </c>
       <c r="H59" t="s">
+        <v>305</v>
+      </c>
+      <c r="I59" t="s">
         <v>306</v>
-      </c>
-      <c r="I59" t="s">
-        <v>307</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -4108,36 +4120,36 @@
         <v>22</v>
       </c>
       <c r="N59" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O59" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>307</v>
+      </c>
+      <c r="B60" t="s">
         <v>308</v>
-      </c>
-      <c r="B60" t="s">
-        <v>309</v>
       </c>
       <c r="C60" t="s">
         <v>115</v>
       </c>
       <c r="D60" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
       </c>
       <c r="F60" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G60" t="s">
         <v>19</v>
       </c>
       <c r="H60" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
@@ -4155,36 +4167,36 @@
         <v>22</v>
       </c>
       <c r="N60" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O60" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B61" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C61" t="s">
         <v>115</v>
       </c>
       <c r="D61" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
       </c>
       <c r="F61" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G61" t="s">
         <v>19</v>
       </c>
       <c r="H61" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
@@ -4202,10 +4214,57 @@
         <v>22</v>
       </c>
       <c r="N61" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O61" t="s">
-        <v>312</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>315</v>
+      </c>
+      <c r="B62" t="s">
+        <v>174</v>
+      </c>
+      <c r="C62" t="s">
+        <v>175</v>
+      </c>
+      <c r="D62" t="s">
+        <v>316</v>
+      </c>
+      <c r="E62" t="s">
+        <v>317</v>
+      </c>
+      <c r="F62" t="s">
+        <v>316</v>
+      </c>
+      <c r="G62" t="s">
+        <v>317</v>
+      </c>
+      <c r="H62" t="s">
+        <v>318</v>
+      </c>
+      <c r="I62" t="s">
+        <v>319</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62" t="s">
+        <v>21</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62" t="s">
+        <v>22</v>
+      </c>
+      <c r="N62" t="s">
+        <v>179</v>
+      </c>
+      <c r="O62" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
